--- a/customer_service_forms/023_customer_gift_assistance_contact_form--customer_service_forms.xlsx
+++ b/customer_service_forms/023_customer_gift_assistance_contact_form--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'gift_card'}</t>
+          <t>gift_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Gift Card'}</t>
+          <t>Gift Card</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'product'}</t>
+          <t>product</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Product'}</t>
+          <t>Product</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'visa'}</t>
+          <t>visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Visa'}</t>
+          <t>Visa</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'mastercard'}</t>
+          <t>mastercard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Mastercard'}</t>
+          <t>Mastercard</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'discover'}</t>
+          <t>discover</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Discover'}</t>
+          <t>Discover</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'amex'}</t>
+          <t>amex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Amex'}</t>
+          <t>Amex</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'amazon'}</t>
+          <t>amazon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Amazon'}</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'ebay'}</t>
+          <t>ebay</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'eBay'}</t>
+          <t>eBay</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
